--- a/artfynd/A 5171-2026 artfynd.xlsx
+++ b/artfynd/A 5171-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95786136</v>
+        <v>95785272</v>
       </c>
       <c r="B2" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>5964</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>476910.8644376132</v>
+        <v>476859</v>
       </c>
       <c r="R2" t="n">
-        <v>7001622.441445032</v>
+        <v>7001775</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,24 +744,9 @@
           <t>2021-08-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,19 +773,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95785272</v>
+        <v>95785633</v>
       </c>
       <c r="B3" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -818,12 +793,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -834,10 +809,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>476858.9751439748</v>
+        <v>476912</v>
       </c>
       <c r="R3" t="n">
-        <v>7001774.741748242</v>
+        <v>7001670</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,19 +842,9 @@
           <t>2021-08-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,16 +874,11 @@
         <v>95786036</v>
       </c>
       <c r="B4" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -931,12 +891,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>476894.6320846474</v>
+        <v>476895</v>
       </c>
       <c r="R4" t="n">
-        <v>7001632.053086182</v>
+        <v>7001632</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +940,9 @@
           <t>2021-08-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,37 +969,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95786435</v>
+        <v>95786337</v>
       </c>
       <c r="B5" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93233</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>5964</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1060,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>476928.4616858959</v>
+        <v>476931</v>
       </c>
       <c r="R5" t="n">
-        <v>7001486.658411626</v>
+        <v>7001507</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1093,24 +1038,9 @@
           <t>2021-08-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På sälg</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95786337</v>
+        <v>95786136</v>
       </c>
       <c r="B6" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,21 +1078,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5964</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>476931.320268895</v>
+        <v>476911</v>
       </c>
       <c r="R6" t="n">
-        <v>7001506.534836936</v>
+        <v>7001622</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1211,19 +1136,14 @@
           <t>2021-08-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-08-29</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,15 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95786429</v>
+        <v>95786435</v>
       </c>
       <c r="B7" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,21 +1181,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1291,10 +1206,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>476928.4616858959</v>
+        <v>476929</v>
       </c>
       <c r="R7" t="n">
-        <v>7001486.658411626</v>
+        <v>7001487</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1324,19 +1239,9 @@
           <t>2021-08-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1368,15 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>95785633</v>
+        <v>129875334</v>
       </c>
       <c r="B8" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99022</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,38 +1284,41 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5964</v>
+        <v>220093</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>Châtel.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Fillstabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>476911.1998536056</v>
+        <v>477117</v>
       </c>
       <c r="R8" t="n">
-        <v>7001669.465686922</v>
+        <v>7001569</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,22 +1342,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,27 +1362,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>95786131</v>
+        <v>129875333</v>
       </c>
       <c r="B9" t="n">
-        <v>78527</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1497,38 +1389,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229497</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Fillstabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>476910.8644376132</v>
+        <v>477133</v>
       </c>
       <c r="R9" t="n">
-        <v>7001622.441445032</v>
+        <v>7001568</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1552,27 +1443,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-08-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På sälg</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1587,22 +1463,26 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Anton Gårdman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Anton Gårdman</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129875334</v>
+        <v>95786131</v>
       </c>
       <c r="B10" t="n">
-        <v>98737</v>
+        <v>80392</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1610,41 +1490,38 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>229497</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Fillstabäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477117</v>
+        <v>476911</v>
       </c>
       <c r="R10" t="n">
-        <v>7001569</v>
+        <v>7001622</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,12 +1545,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2021-08-29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-09</t>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,19 +1570,118 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anton Gårdman</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>NNK kartering 2025, Länsstyrelsen Jämtlands län.</t>
-        </is>
-      </c>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>95786429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Fillstabäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>476929</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7001487</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Frösö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-08-29</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På sälg</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
